--- a/ket_qua_Q.xlsx
+++ b/ket_qua_Q.xlsx
@@ -10,7 +10,7 @@
     <sheet name="SAT Q" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SAT Q'!$A$1:$G$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SAT Q'!$A$1:$G$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -509,7 +509,7 @@
         <v>146</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.000386</v>
+        <v>0.000402</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>8</v>
@@ -536,7 +536,7 @@
         <v>968</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.0054</v>
+        <v>0.002065</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>17</v>
@@ -563,7 +563,7 @@
         <v>5184</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.025098</v>
+        <v>0.012782</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>32</v>
@@ -590,7 +590,7 @@
         <v>24832</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.08118599999999999</v>
+        <v>0.053838</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>57</v>
@@ -617,7 +617,7 @@
         <v>112608</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.384301</v>
+        <v>0.258488</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>100</v>
@@ -628,8 +628,116 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Q_7</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>22656</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>500096</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1.1702</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Q_8</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>256</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>81920</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2216192</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>7.37378</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Q_9</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>512</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>303616</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>9878528</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>31.78986</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>593</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Q_10</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>1024</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1150976</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>44339712</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>192.396921</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>1124</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>OPT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>